--- a/artfynd/A 54999-2023 artfynd.xlsx
+++ b/artfynd/A 54999-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54999-2023 artfynd.xlsx
+++ b/artfynd/A 54999-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75247213</v>
+        <v>75247212</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433424.8614557533</v>
+        <v>433431</v>
       </c>
       <c r="R2" t="n">
-        <v>6963249.152931729</v>
+        <v>6963187</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2018-06-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-06-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,15 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>omkring 100-årig, blockig tallskog</t>
+          <t>omkring 100-årig, skiktad tallskog</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # murken gammal tallåga</t>
+          <t>3 substratenheter # grova gamla tallågor</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75247212</v>
+        <v>75247213</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433430.9313564155</v>
+        <v>433425</v>
       </c>
       <c r="R3" t="n">
-        <v>6963186.781355315</v>
+        <v>6963249</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,19 +857,9 @@
           <t>2018-06-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-06-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,15 +873,15 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>omkring 100-årig, skiktad tallskog</t>
+          <t>omkring 100-årig, blockig tallskog</t>
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>3 substratenheter # grova gamla tallågor</t>
+          <t>1 substratenheter # murken gammal tallåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -936,12 +906,7 @@
         <v>75247211</v>
       </c>
       <c r="B4" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433438.0476419898</v>
+        <v>433438</v>
       </c>
       <c r="R4" t="n">
-        <v>6963130.795540501</v>
+        <v>6963131</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1006,19 +971,9 @@
           <t>2018-06-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-06-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,12 +1020,7 @@
         <v>75247210</v>
       </c>
       <c r="B5" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433450.1033930159</v>
+        <v>433450</v>
       </c>
       <c r="R5" t="n">
-        <v>6963114.988741904</v>
+        <v>6963115</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1135,19 +1085,9 @@
           <t>2018-06-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-06-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54999-2023 artfynd.xlsx
+++ b/artfynd/A 54999-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247212</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247213</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247211</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,8 +1148,19 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247210</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>